--- a/backend/templates/reportes/Ficha SIGUD audiovisuales.xlsx
+++ b/backend/templates/reportes/Ficha SIGUD audiovisuales.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9758C514-3BC7-408F-B77D-7DD3EC83DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D078B008-BDDF-461A-ABC6-09974EF4A627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
@@ -154,7 +154,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="2" tint="-9.9978637043366805E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -365,9 +364,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -395,9 +391,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -428,38 +457,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,41 +1369,41 @@
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="28" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="29"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="35"/>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="32" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="27"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1422,13 +1421,13 @@
       <c r="C6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="44" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="7"/>
@@ -1444,168 +1443,168 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="12" t="s">
+      <c r="C8" s="32"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="24"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="24"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="24"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="24"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="24"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="24"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="38"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="22"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
@@ -1616,6 +1615,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="C17:F19"/>
     <mergeCell ref="C21:F21"/>
@@ -1625,12 +1630,6 @@
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
